--- a/VerveStacks_FRA_grids_kan25/vt_vervestacks_FRA_v1.xlsx
+++ b/VerveStacks_FRA_grids_kan25/vt_vervestacks_FRA_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_FRA_grids_kan25\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{00BF5899-2096-4363-B99E-F9B8ABA2BEC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0C7B3F51-2C0E-4FB8-A82A-024DC453A0A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{394FC24A-7ACB-4BE1-BAA8-BB6D026F5CBF}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{E49FFBD9-F1C7-4CC8-9281-AD177A315261}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -4102,7 +4102,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35264EF8-76DF-4806-8D2C-6BA825257A60}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4315C565-EA61-40CC-8EE8-C4D960C80B92}">
   <dimension ref="B9:V131"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -11684,7 +11684,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4DBE1173-41FE-446C-A4F8-0F93259EDAD0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1866860E-15CC-407B-911C-3A0B2220C087}">
   <dimension ref="B9:X130"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -18508,7 +18508,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A548CFE1-9155-46B5-B4DC-EA1CEAC68B99}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C31EE69-71DB-41CA-BF62-AFCB6C27F0B1}">
   <dimension ref="B9:X932"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -40254,7 +40254,7 @@
         <v>16</v>
       </c>
       <c r="T373" t="s">
-        <v>850</v>
+        <v>542</v>
       </c>
       <c r="U373" t="s">
         <v>532</v>
@@ -40316,7 +40316,7 @@
         <v>16</v>
       </c>
       <c r="T374" t="s">
-        <v>542</v>
+        <v>850</v>
       </c>
       <c r="U374" t="s">
         <v>532</v>
@@ -40564,7 +40564,7 @@
         <v>16</v>
       </c>
       <c r="T378" t="s">
-        <v>850</v>
+        <v>542</v>
       </c>
       <c r="U378" t="s">
         <v>532</v>
@@ -40626,7 +40626,7 @@
         <v>16</v>
       </c>
       <c r="T379" t="s">
-        <v>542</v>
+        <v>850</v>
       </c>
       <c r="U379" t="s">
         <v>532</v>
@@ -41184,7 +41184,7 @@
         <v>16</v>
       </c>
       <c r="T388" t="s">
-        <v>542</v>
+        <v>850</v>
       </c>
       <c r="U388" t="s">
         <v>532</v>
@@ -41246,7 +41246,7 @@
         <v>16</v>
       </c>
       <c r="T389" t="s">
-        <v>850</v>
+        <v>542</v>
       </c>
       <c r="U389" t="s">
         <v>532</v>
@@ -41804,7 +41804,7 @@
         <v>16</v>
       </c>
       <c r="T398" t="s">
-        <v>850</v>
+        <v>542</v>
       </c>
       <c r="U398" t="s">
         <v>532</v>
@@ -41866,7 +41866,7 @@
         <v>16</v>
       </c>
       <c r="T399" t="s">
-        <v>542</v>
+        <v>850</v>
       </c>
       <c r="U399" t="s">
         <v>532</v>
@@ -42610,7 +42610,7 @@
         <v>16</v>
       </c>
       <c r="T411" t="s">
-        <v>542</v>
+        <v>850</v>
       </c>
       <c r="U411" t="s">
         <v>532</v>
@@ -42672,7 +42672,7 @@
         <v>16</v>
       </c>
       <c r="T412" t="s">
-        <v>850</v>
+        <v>542</v>
       </c>
       <c r="U412" t="s">
         <v>532</v>
@@ -42734,7 +42734,7 @@
         <v>16</v>
       </c>
       <c r="T413" t="s">
-        <v>850</v>
+        <v>542</v>
       </c>
       <c r="U413" t="s">
         <v>532</v>
@@ -42796,7 +42796,7 @@
         <v>16</v>
       </c>
       <c r="T414" t="s">
-        <v>542</v>
+        <v>850</v>
       </c>
       <c r="U414" t="s">
         <v>532</v>
@@ -53437,7 +53437,7 @@
         <v>33</v>
       </c>
       <c r="O687">
-        <v>0.48643306459259261</v>
+        <v>0.48643306459259256</v>
       </c>
     </row>
     <row r="688" spans="2:15" x14ac:dyDescent="0.45">
@@ -53466,7 +53466,7 @@
         <v>33</v>
       </c>
       <c r="O688">
-        <v>0.48643306459259261</v>
+        <v>0.48643306459259256</v>
       </c>
     </row>
     <row r="689" spans="2:15" x14ac:dyDescent="0.45">
@@ -53495,7 +53495,7 @@
         <v>33</v>
       </c>
       <c r="O689">
-        <v>0.48643306459259261</v>
+        <v>0.48643306459259256</v>
       </c>
     </row>
     <row r="690" spans="2:15" x14ac:dyDescent="0.45">
@@ -62720,7 +62720,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8526C16B-C9CB-4869-95D6-54CAE4F945A1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8311937-094A-4A2A-89C8-D3731675B70B}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>
